--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.0668</v>
+        <v>17.10727</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49632</v>
+        <v>16.65905</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53483</v>
+        <v>16.85091</v>
       </c>
       <c r="F2" t="n">
-        <v>42.74922</v>
+        <v>42.90593</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05026</v>
+        <v>0.05082</v>
       </c>
       <c r="H2" t="n">
-        <v>1.848</v>
+        <v>1.79428</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.90202</v>
+        <v>17.07436</v>
       </c>
       <c r="D3" t="n">
-        <v>16.68566</v>
+        <v>16.25654</v>
       </c>
       <c r="E3" t="n">
-        <v>16.69284</v>
+        <v>16.31801</v>
       </c>
       <c r="F3" t="n">
-        <v>43.10449</v>
+        <v>42.88873</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05089</v>
+        <v>0.04989</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81602</v>
+        <v>1.83253</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.01882</v>
+        <v>16.78985</v>
       </c>
       <c r="D4" t="n">
-        <v>16.53556</v>
+        <v>16.5107</v>
       </c>
       <c r="E4" t="n">
-        <v>16.53171</v>
+        <v>16.71024</v>
       </c>
       <c r="F4" t="n">
-        <v>42.94916</v>
+        <v>42.49661</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05008</v>
+        <v>0.05063</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83865</v>
+        <v>1.76794</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.55599</v>
+        <v>16.89108</v>
       </c>
       <c r="D6" t="n">
-        <v>16.02339</v>
+        <v>16.01392</v>
       </c>
       <c r="E6" t="n">
-        <v>16.18876</v>
+        <v>16.21767</v>
       </c>
       <c r="F6" t="n">
-        <v>22.48204</v>
+        <v>21.75669</v>
       </c>
       <c r="G6" t="n">
-        <v>33.97781</v>
+        <v>34.56992</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.91078</v>
+        <v>16.61504</v>
       </c>
       <c r="D7" t="n">
-        <v>15.94211</v>
+        <v>15.78516</v>
       </c>
       <c r="E7" t="n">
-        <v>16.54922</v>
+        <v>16.21709</v>
       </c>
       <c r="F7" t="n">
-        <v>21.66139</v>
+        <v>21.81047</v>
       </c>
       <c r="G7" t="n">
-        <v>34.79007</v>
+        <v>34.45975</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.67368</v>
+        <v>16.77346</v>
       </c>
       <c r="D8" t="n">
-        <v>16.28837</v>
+        <v>16.16102</v>
       </c>
       <c r="E8" t="n">
-        <v>16.55792</v>
+        <v>16.4486</v>
       </c>
       <c r="F8" t="n">
-        <v>21.69287</v>
+        <v>21.97394</v>
       </c>
       <c r="G8" t="n">
-        <v>34.20448</v>
+        <v>33.85479</v>
       </c>
     </row>
   </sheetData>
